--- a/parameters/UA/ammonia/demand_parameters.xlsx
+++ b/parameters/UA/ammonia/demand_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\ammonia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/engs2859_ox_ac_uk/Documents/Geo-X/Geo-X/parameters/UA/ammonia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29AA16E-D8D8-46F9-86F9-5656102FF9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{55A59CC4-7BED-4A7D-97DF-16C229342A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89B6A140-E854-0044-9536-3607FA4F38A3}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{1EFB3969-2EEE-7045-9FD0-00480E0E3DAF}"/>
+    <workbookView xWindow="780" yWindow="800" windowWidth="18900" windowHeight="10960" xr2:uid="{1EFB3969-2EEE-7045-9FD0-00480E0E3DAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand centers" sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
     <t>Demand state</t>
   </si>
   <si>
-    <t>Kyiv</t>
+    <t>Odessa</t>
   </si>
 </sst>
 </file>
@@ -63,8 +63,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
@@ -108,15 +108,14 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -134,6 +133,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,50 +437,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21CD761-0C02-5F48-878C-D5E4B46C4E1D}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="41.375" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="22.375" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
-        <v>50.42</v>
-      </c>
-      <c r="C2" s="3">
-        <v>30.58</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1000000000</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="B2" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>30.75</v>
+      </c>
+      <c r="D2">
+        <v>100000000</v>
+      </c>
+      <c r="E2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D7" s="1"/>
     </row>
   </sheetData>
